--- a/SourceData/Datas/__enums__.xlsx
+++ b/SourceData/Datas/__enums__.xlsx
@@ -1012,7 +1012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L30"/>
+  <dimension ref="A1:L36"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="23.125" customWidth="1" style="1" min="2" max="2"/>
@@ -1470,217 +1470,317 @@
       <c r="K18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Flag</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>剧情旗标</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>10</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>param=flagId</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>GotoAction</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>GotoAction</t>
         </is>
       </c>
-      <c r="C19" t="b">
+      <c r="C20" t="b">
         <v>0</v>
       </c>
-      <c r="D19" t="b">
+      <c r="D20" t="b">
         <v>1</v>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>引导动作</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>无动作</t>
         </is>
       </c>
-      <c r="J19" t="n">
+      <c r="J20" t="n">
         <v>0</v>
-      </c>
-      <c r="K19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>OpenCraft</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>打开工作台</t>
-        </is>
-      </c>
-      <c r="J20" t="n">
-        <v>1</v>
       </c>
       <c r="K20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="H21" t="inlineStr">
         <is>
-          <t>SelectHoe</t>
+          <t>OpenCraft</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>选中锄头</t>
+          <t>打开工作台</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="H22" t="inlineStr">
         <is>
-          <t>SelectSeeds</t>
+          <t>SelectHoe</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>选中种子</t>
+          <t>选中锄头</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="H23" t="inlineStr">
         <is>
-          <t>SelectCan</t>
+          <t>SelectSeeds</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>选中水壶</t>
+          <t>选中种子</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="H24" t="inlineStr">
         <is>
-          <t>SelectHand</t>
+          <t>SelectCan</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>选中手</t>
+          <t>选中水壶</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="H25" t="inlineStr">
         <is>
-          <t>SelectRod</t>
+          <t>SelectHand</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>选中鱼竿</t>
+          <t>选中手</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="H26" t="inlineStr">
         <is>
-          <t>OpenBag</t>
+          <t>SelectRod</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>打开背包</t>
+          <t>选中鱼竿</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="H27" t="inlineStr">
         <is>
-          <t>HintFarm</t>
+          <t>OpenBag</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>提示农田</t>
+          <t>打开背包</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="H28" t="inlineStr">
         <is>
-          <t>HintGrass</t>
+          <t>HintFarm</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>提示杂草</t>
+          <t>提示农田</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="H29" t="inlineStr">
         <is>
-          <t>HintFish</t>
+          <t>HintGrass</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>提示钓鱼</t>
+          <t>提示杂草</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="H30" t="inlineStr">
         <is>
+          <t>HintFish</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>提示钓鱼</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>10</v>
+      </c>
+      <c r="K30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="H31" t="inlineStr">
+        <is>
           <t>HintCraft</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>提示工作台</t>
         </is>
       </c>
-      <c r="J30" t="n">
+      <c r="J31" t="n">
         <v>11</v>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>HintMeteor</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>提示通往小镇（旧）</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>12</v>
+      </c>
+      <c r="K32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>HintTownGate</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>提示通往小镇的路牌</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>13</v>
+      </c>
+      <c r="K33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>HintMayor</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>提示镇长府</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>14</v>
+      </c>
+      <c r="K34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>SelectAxe</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>选中斧头</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>15</v>
+      </c>
+      <c r="K35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>HintRock</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>提示挖石</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>16</v>
+      </c>
+      <c r="K36" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/SourceData/Datas/__enums__.xlsx
+++ b/SourceData/Datas/__enums__.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="29340" windowHeight="14540" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="144525" fullCalcOnLoad="1" calcCompleted="0" calcOnSave="0"/>

--- a/SourceData/Datas/__enums__.xlsx
+++ b/SourceData/Datas/__enums__.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="29340" windowHeight="14540" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="144525" fullCalcOnLoad="1" calcCompleted="0" calcOnSave="0"/>
@@ -1012,7 +1012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L36"/>
+  <dimension ref="A1:L44"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="23.125" customWidth="1" style="1" min="2" max="2"/>
@@ -1153,634 +1153,783 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="0" t="inlineStr">
         <is>
           <t>ConditionOperatorType</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="0" t="inlineStr">
         <is>
           <t>ConditionOperatorType</t>
         </is>
       </c>
-      <c r="C4" t="b">
+      <c r="C4" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="D4" t="b">
+      <c r="D4" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="0" t="inlineStr">
         <is>
           <t>条件比较操作符</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" s="0" t="inlineStr">
         <is>
           <t>Less</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I4" s="0" t="inlineStr">
         <is>
           <t>小于</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="J4" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K4" s="0" t="inlineStr">
         <is>
           <t>&lt;</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="H5" t="inlineStr">
+      <c r="H5" s="0" t="inlineStr">
         <is>
           <t>Greater</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I5" s="0" t="inlineStr">
         <is>
           <t>大于</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="J5" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K5" s="0" t="inlineStr">
         <is>
           <t>&gt;</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="H6" t="inlineStr">
+      <c r="H6" s="0" t="inlineStr">
         <is>
           <t>LessEqual</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I6" s="0" t="inlineStr">
         <is>
           <t>小于等于</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="J6" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K6" s="0" t="inlineStr">
         <is>
           <t>&lt;=</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="H7" t="inlineStr">
+      <c r="H7" s="0" t="inlineStr">
         <is>
           <t>GreaterEqual</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I7" s="0" t="inlineStr">
         <is>
           <t>大于等于</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="J7" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K7" s="0" t="inlineStr">
         <is>
           <t>&gt;=</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="H8" t="inlineStr">
+      <c r="H8" s="0" t="inlineStr">
         <is>
           <t>Equal</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I8" s="0" t="inlineStr">
         <is>
           <t>等于</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="J8" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="K8">
+      <c r="K8" s="0">
         <f>=</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="H9" t="inlineStr">
+      <c r="H9" s="0" t="inlineStr">
         <is>
           <t>NotEqual</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I9" s="0" t="inlineStr">
         <is>
           <t>不等于</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="J9" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K9" s="0" t="inlineStr">
         <is>
           <t>!=</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="0" t="inlineStr">
         <is>
           <t>ConditionType</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="0" t="inlineStr">
         <is>
           <t>ConditionType</t>
         </is>
       </c>
-      <c r="C10" t="b">
+      <c r="C10" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="D10" t="b">
+      <c r="D10" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" s="0" t="inlineStr">
         <is>
           <t>条件数据源</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H10" s="0" t="inlineStr">
         <is>
           <t>ItemCount</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I10" s="0" t="inlineStr">
         <is>
           <t>背包数量</t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="J10" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="K10" s="0" t="inlineStr">
         <is>
           <t>param=itemId</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="H11" t="inlineStr">
+      <c r="H11" s="0" t="inlineStr">
         <is>
           <t>GatherCount</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I11" s="0" t="inlineStr">
         <is>
           <t>累计采集</t>
         </is>
       </c>
-      <c r="J11" t="n">
+      <c r="J11" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K11" s="0" t="inlineStr">
         <is>
           <t>param=itemId</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="H12" t="inlineStr">
+      <c r="H12" s="0" t="inlineStr">
         <is>
           <t>TillCount</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I12" s="0" t="inlineStr">
         <is>
           <t>累计锄地</t>
         </is>
       </c>
-      <c r="J12" t="n">
+      <c r="J12" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" s="0" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="H13" t="inlineStr">
+      <c r="H13" s="0" t="inlineStr">
         <is>
           <t>PlantCount</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I13" s="0" t="inlineStr">
         <is>
           <t>累计播种</t>
         </is>
       </c>
-      <c r="J13" t="n">
+      <c r="J13" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" s="0" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="H14" t="inlineStr">
+      <c r="H14" s="0" t="inlineStr">
         <is>
           <t>WaterCount</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="I14" s="0" t="inlineStr">
         <is>
           <t>累计浇水</t>
         </is>
       </c>
-      <c r="J14" t="n">
+      <c r="J14" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" s="0" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="H15" t="inlineStr">
+      <c r="H15" s="0" t="inlineStr">
         <is>
           <t>HarvestCount</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="I15" s="0" t="inlineStr">
         <is>
           <t>累计收获</t>
         </is>
       </c>
-      <c r="J15" t="n">
+      <c r="J15" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" s="0" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="H16" t="inlineStr">
+      <c r="H16" s="0" t="inlineStr">
         <is>
           <t>CraftCount</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="I16" s="0" t="inlineStr">
         <is>
           <t>累计合成</t>
         </is>
       </c>
-      <c r="J16" t="n">
+      <c r="J16" s="0" t="n">
         <v>7</v>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="K16" s="0" t="inlineStr">
         <is>
           <t>param=recipeId</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="H17" t="inlineStr">
+      <c r="H17" s="0" t="inlineStr">
         <is>
           <t>FishCount</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="I17" s="0" t="inlineStr">
         <is>
           <t>累计钓鱼</t>
         </is>
       </c>
-      <c r="J17" t="n">
+      <c r="J17" s="0" t="n">
         <v>8</v>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" s="0" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="H18" t="inlineStr">
+      <c r="H18" s="0" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="I18" s="0" t="inlineStr">
         <is>
           <t>金币数量</t>
         </is>
       </c>
-      <c r="J18" t="n">
+      <c r="J18" s="0" t="n">
         <v>9</v>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" s="0" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="H19" t="inlineStr">
+      <c r="H19" s="0" t="inlineStr">
         <is>
           <t>Flag</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="I19" s="0" t="inlineStr">
         <is>
           <t>剧情旗标</t>
         </is>
       </c>
-      <c r="J19" t="n">
+      <c r="J19" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="K19" s="0" t="inlineStr">
         <is>
           <t>param=flagId</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="0" t="inlineStr">
         <is>
           <t>GotoAction</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="0" t="inlineStr">
         <is>
           <t>GotoAction</t>
         </is>
       </c>
-      <c r="C20" t="b">
+      <c r="C20" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="D20" t="b">
+      <c r="D20" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F20" s="0" t="inlineStr">
         <is>
           <t>引导动作</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="H20" s="0" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="I20" s="0" t="inlineStr">
         <is>
           <t>无动作</t>
         </is>
       </c>
-      <c r="J20" t="n">
+      <c r="J20" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" s="0" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="H21" t="inlineStr">
+      <c r="H21" s="0" t="inlineStr">
         <is>
           <t>OpenCraft</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="I21" s="0" t="inlineStr">
         <is>
           <t>打开工作台</t>
         </is>
       </c>
-      <c r="J21" t="n">
+      <c r="J21" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" s="0" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="H22" t="inlineStr">
+      <c r="H22" s="0" t="inlineStr">
         <is>
           <t>SelectHoe</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="I22" s="0" t="inlineStr">
         <is>
           <t>选中锄头</t>
         </is>
       </c>
-      <c r="J22" t="n">
+      <c r="J22" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" s="0" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="H23" t="inlineStr">
+      <c r="H23" s="0" t="inlineStr">
         <is>
           <t>SelectSeeds</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="I23" s="0" t="inlineStr">
         <is>
           <t>选中种子</t>
         </is>
       </c>
-      <c r="J23" t="n">
+      <c r="J23" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" s="0" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="H24" t="inlineStr">
+      <c r="H24" s="0" t="inlineStr">
         <is>
           <t>SelectCan</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="I24" s="0" t="inlineStr">
         <is>
           <t>选中水壶</t>
         </is>
       </c>
-      <c r="J24" t="n">
+      <c r="J24" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" s="0" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="H25" t="inlineStr">
+      <c r="H25" s="0" t="inlineStr">
         <is>
           <t>SelectHand</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="I25" s="0" t="inlineStr">
         <is>
           <t>选中手</t>
         </is>
       </c>
-      <c r="J25" t="n">
+      <c r="J25" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" s="0" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="H26" t="inlineStr">
+      <c r="H26" s="0" t="inlineStr">
         <is>
           <t>SelectRod</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="I26" s="0" t="inlineStr">
         <is>
           <t>选中鱼竿</t>
         </is>
       </c>
-      <c r="J26" t="n">
+      <c r="J26" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" s="0" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="H27" t="inlineStr">
+      <c r="H27" s="0" t="inlineStr">
         <is>
           <t>OpenBag</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="I27" s="0" t="inlineStr">
         <is>
           <t>打开背包</t>
         </is>
       </c>
-      <c r="J27" t="n">
+      <c r="J27" s="0" t="n">
         <v>7</v>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" s="0" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="H28" t="inlineStr">
+      <c r="H28" s="0" t="inlineStr">
         <is>
           <t>HintFarm</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="I28" s="0" t="inlineStr">
         <is>
           <t>提示农田</t>
         </is>
       </c>
-      <c r="J28" t="n">
+      <c r="J28" s="0" t="n">
         <v>8</v>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" s="0" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="H29" t="inlineStr">
+      <c r="H29" s="0" t="inlineStr">
         <is>
           <t>HintGrass</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="I29" s="0" t="inlineStr">
         <is>
           <t>提示杂草</t>
         </is>
       </c>
-      <c r="J29" t="n">
+      <c r="J29" s="0" t="n">
         <v>9</v>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" s="0" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="H30" t="inlineStr">
+      <c r="H30" s="0" t="inlineStr">
         <is>
           <t>HintFish</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="I30" s="0" t="inlineStr">
         <is>
           <t>提示钓鱼</t>
         </is>
       </c>
-      <c r="J30" t="n">
+      <c r="J30" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" s="0" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="H31" t="inlineStr">
+      <c r="H31" s="0" t="inlineStr">
         <is>
           <t>HintCraft</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="I31" s="0" t="inlineStr">
         <is>
           <t>提示工作台</t>
         </is>
       </c>
-      <c r="J31" t="n">
+      <c r="J31" s="0" t="n">
         <v>11</v>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" s="0" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="H32" t="inlineStr">
+      <c r="H32" s="0" t="inlineStr">
         <is>
           <t>HintMeteor</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="I32" s="0" t="inlineStr">
         <is>
           <t>提示通往小镇（旧）</t>
         </is>
       </c>
-      <c r="J32" t="n">
+      <c r="J32" s="0" t="n">
         <v>12</v>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" s="0" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="H33" t="inlineStr">
+      <c r="H33" s="0" t="inlineStr">
         <is>
           <t>HintTownGate</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="I33" s="0" t="inlineStr">
         <is>
           <t>提示通往小镇的路牌</t>
         </is>
       </c>
-      <c r="J33" t="n">
+      <c r="J33" s="0" t="n">
         <v>13</v>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" s="0" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="H34" t="inlineStr">
+      <c r="H34" s="0" t="inlineStr">
         <is>
           <t>HintMayor</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="I34" s="0" t="inlineStr">
         <is>
           <t>提示镇长府</t>
         </is>
       </c>
-      <c r="J34" t="n">
+      <c r="J34" s="0" t="n">
         <v>14</v>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" s="0" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="H35" t="inlineStr">
+      <c r="H35" s="0" t="inlineStr">
         <is>
           <t>SelectAxe</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="I35" s="0" t="inlineStr">
         <is>
           <t>选中斧头</t>
         </is>
       </c>
-      <c r="J35" t="n">
+      <c r="J35" s="0" t="n">
         <v>15</v>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" s="0" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="H36" t="inlineStr">
+      <c r="H36" s="0" t="inlineStr">
         <is>
           <t>HintRock</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="I36" s="0" t="inlineStr">
         <is>
           <t>提示挖石</t>
         </is>
       </c>
-      <c r="J36" t="n">
+      <c r="J36" s="0" t="n">
         <v>16</v>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" s="0" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>ItemType</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>ItemType</t>
+        </is>
+      </c>
+      <c r="C37" t="b">
+        <v>0</v>
+      </c>
+      <c r="D37" t="b">
+        <v>1</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>物品类型</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Misc</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>杂项</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Tool</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>工具</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>1</v>
+      </c>
+      <c r="K38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>材料</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>2</v>
+      </c>
+      <c r="K39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Consumable</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>消耗品</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>3</v>
+      </c>
+      <c r="K40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>货币</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>4</v>
+      </c>
+      <c r="K41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Crop</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>作物</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>5</v>
+      </c>
+      <c r="K42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Recipe</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>配方</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>6</v>
+      </c>
+      <c r="K43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Seed</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>种子</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
+        <v>7</v>
+      </c>
+      <c r="K44" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
